--- a/public/sample_questions.xlsx
+++ b/public/sample_questions.xlsx
@@ -397,19 +397,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:N6"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="46.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
-    <col min="11" max="11" width="44.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="50.83203125" customWidth="1"/>
+    <col min="14" max="14" width="44.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -417,33 +420,42 @@
         <v>問題番号</v>
       </c>
       <c r="B1" t="str">
+        <v>科目</v>
+      </c>
+      <c r="C1" t="str">
+        <v>タグ</v>
+      </c>
+      <c r="D1" t="str">
         <v>問題文</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>下線キーワード</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>画像URL</v>
+      </c>
+      <c r="G1" t="str">
         <v>選択肢a</v>
       </c>
-      <c r="E1" t="str">
+      <c r="H1" t="str">
         <v>選択肢b</v>
       </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>選択肢c</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>選択肢d</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>選択肢e</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>正解</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>解説</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>基本事項</v>
       </c>
     </row>
@@ -452,33 +464,42 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
+        <v>循環器</v>
+      </c>
+      <c r="C2" t="str">
+        <v>心電図、虚血性心疾患</v>
+      </c>
+      <c r="D2" t="str">
         <v>急性心筋梗塞の発症直後（超急性期）にみられる心電図変化として、最も特徴的なのはどれか。</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>超急性期、心電図変化</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>ST上昇</v>
       </c>
-      <c r="E2" t="str">
+      <c r="H2" t="str">
         <v>異常Q波の出現</v>
       </c>
-      <c r="F2" t="str">
+      <c r="I2" t="str">
         <v>T波の陰転化</v>
       </c>
-      <c r="G2" t="str">
+      <c r="J2" t="str">
         <v>PQ間隔の延長</v>
       </c>
-      <c r="H2" t="str">
+      <c r="K2" t="str">
         <v>U波の出現</v>
       </c>
-      <c r="I2" t="str">
+      <c r="L2" t="str">
         <v>a</v>
       </c>
-      <c r="J2" t="str">
+      <c r="M2" t="str">
         <v>急性心筋梗塞の超急性期には、障害を受けた心筋領域に一致した誘導でST上昇が最初に出現する。異常Q波やT波の陰転化は、より後の時期（急性期〜亜急性期）にみられる所見である。</v>
       </c>
-      <c r="K2" t="str" xml:space="preserve">
+      <c r="N2" t="str" xml:space="preserve">
         <v xml:space="preserve">ST上昇 → 異常Q波 → 陰転化したT波、という経時的変化を覚える
 ST上昇は障害心筋に一致した誘導に出現する
 異常Q波は不可逆的な心筋壊死を反映する</v>
@@ -489,33 +510,42 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
+        <v>消化器</v>
+      </c>
+      <c r="C3" t="str">
+        <v>肝臓、生理学</v>
+      </c>
+      <c r="D3" t="str">
         <v>肝臓の機能に関する記述のうち、誤っているのはどれか。</v>
       </c>
-      <c r="C3" t="str">
+      <c r="E3" t="str">
         <v>肝臓の機能</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
         <v>アルブミンを合成する</v>
       </c>
-      <c r="E3" t="str">
+      <c r="H3" t="str">
         <v>胆汁を生成する</v>
       </c>
-      <c r="F3" t="str">
+      <c r="I3" t="str">
         <v>胆汁を貯留する</v>
       </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
         <v>アンモニアを尿素に変換する</v>
       </c>
-      <c r="H3" t="str">
+      <c r="K3" t="str">
         <v>薬物を代謝する</v>
       </c>
-      <c r="I3" t="str">
+      <c r="L3" t="str">
         <v>c</v>
       </c>
-      <c r="J3" t="str">
+      <c r="M3" t="str">
         <v>胆汁は肝細胞で生成されるが、貯留し濃縮するのは胆嚢の役割である。肝臓はアルブミン合成、尿素回路によるアンモニア処理、薬物代謝など多彩な機能を担う。</v>
       </c>
-      <c r="K3" t="str" xml:space="preserve">
+      <c r="N3" t="str" xml:space="preserve">
         <v xml:space="preserve">胆汁の生成は肝臓、貯留・濃縮は胆嚢と区別する
 肝臓は合成・解毒・代謝の中心臓器
 アンモニアは尿素回路で尿素に変換され腎から排泄される</v>
@@ -526,33 +556,42 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
+        <v>代謝・内分泌</v>
+      </c>
+      <c r="C4" t="str">
+        <v>糖尿病、検査値</v>
+      </c>
+      <c r="D4" t="str">
         <v>空腹時血糖値が糖尿病型と判定される基準値はどれか。</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E4" t="str">
         <v>空腹時血糖値</v>
       </c>
-      <c r="D4" t="str">
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
         <v>100 mg/dL以上</v>
       </c>
-      <c r="E4" t="str">
+      <c r="H4" t="str">
         <v>110 mg/dL以上</v>
       </c>
-      <c r="F4" t="str">
+      <c r="I4" t="str">
         <v>126 mg/dL以上</v>
       </c>
-      <c r="G4" t="str">
+      <c r="J4" t="str">
         <v>140 mg/dL以上</v>
       </c>
-      <c r="H4" t="str">
+      <c r="K4" t="str">
         <v>200 mg/dL以上</v>
       </c>
-      <c r="I4" t="str">
+      <c r="L4" t="str">
         <v>c</v>
       </c>
-      <c r="J4" t="str">
+      <c r="M4" t="str">
         <v>空腹時血糖値126 mg/dL以上、または75gOGTT2時間値200 mg/dL以上、随時血糖値200 mg/dL以上のいずれかを満たす場合を糖尿病型と判定する。</v>
       </c>
-      <c r="K4" t="str" xml:space="preserve">
+      <c r="N4" t="str" xml:space="preserve">
         <v xml:space="preserve">空腹時血糖126以上／OGTT2時間値200以上／随時血糖200以上のいずれかで糖尿病型
 正常型は空腹時110未満かつOGTT2時間値140未満
 境界型はそのいずれにも属さない中間域</v>
@@ -563,41 +602,96 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
+        <v>薬理</v>
+      </c>
+      <c r="C5" t="str">
+        <v>抗菌薬、副作用</v>
+      </c>
+      <c r="D5" t="str">
         <v>アミノグリコシド系抗菌薬で頻度の高い重大な副作用はどれか。</v>
       </c>
-      <c r="C5" t="str">
+      <c r="E5" t="str">
         <v>アミノグリコシド系抗菌薬</v>
       </c>
-      <c r="D5" t="str">
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
         <v>腎障害・第8脳神経障害</v>
       </c>
-      <c r="E5" t="str">
+      <c r="H5" t="str">
         <v>肝障害</v>
       </c>
-      <c r="F5" t="str">
+      <c r="I5" t="str">
         <v>骨髄抑制</v>
       </c>
-      <c r="G5" t="str">
+      <c r="J5" t="str">
         <v>光線過敏症</v>
       </c>
-      <c r="H5" t="str">
+      <c r="K5" t="str">
         <v>消化管出血</v>
       </c>
-      <c r="I5" t="str">
+      <c r="L5" t="str">
         <v>a</v>
       </c>
-      <c r="J5" t="str">
+      <c r="M5" t="str">
         <v>アミノグリコシド系抗菌薬は腎尿細管への蓄積による腎障害と、内耳への蓄積による第8脳神経障害（聴力障害・平衡障害）が代表的な副作用である。</v>
       </c>
-      <c r="K5" t="str" xml:space="preserve">
+      <c r="N5" t="str" xml:space="preserve">
         <v xml:space="preserve">腎機能と聴力のモニタリングが投与中に重要
 血中濃度モニタリング（TDM）の対象薬
 高齢者・腎機能低下患者では特に注意</v>
       </c>
     </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>呼吸器</v>
+      </c>
+      <c r="C6" t="str">
+        <v>喘息、治療</v>
+      </c>
+      <c r="D6" t="str">
+        <v>気管支喘息の長期管理薬として適切なのはどれか。2つ選べ。</v>
+      </c>
+      <c r="E6" t="str">
+        <v>長期管理薬</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>吸入ステロイド薬</v>
+      </c>
+      <c r="H6" t="str">
+        <v>短時間作用性β2刺激薬</v>
+      </c>
+      <c r="I6" t="str">
+        <v>ロイコトリエン受容体拮抗薬</v>
+      </c>
+      <c r="J6" t="str">
+        <v>アドレナリン皮下注射</v>
+      </c>
+      <c r="K6" t="str">
+        <v>生理食塩水吸入</v>
+      </c>
+      <c r="L6" t="str">
+        <v>a、c</v>
+      </c>
+      <c r="M6" t="str">
+        <v>長期管理薬（コントローラー）の中心は吸入ステロイド薬であり、ロイコトリエン受容体拮抗薬も併用される。短時間作用性β2刺激薬やアドレナリンは発作時に使う発作治療薬（リリーバー）である。</v>
+      </c>
+      <c r="N6" t="str" xml:space="preserve">
+        <v xml:space="preserve">長期管理薬（コントローラー）と発作治療薬（リリーバー）を区別する
+吸入ステロイド薬が長期管理の基本
+短時間作用性β2刺激薬の使用頻度はコントロール状態の指標になる</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/sample_questions.xlsx
+++ b/public/sample_questions.xlsx
@@ -397,22 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:M6"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="46.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" customWidth="1"/>
-    <col min="13" max="13" width="50.83203125" customWidth="1"/>
-    <col min="14" max="14" width="44.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="12" max="12" width="50.83203125" customWidth="1"/>
+    <col min="13" max="13" width="44.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,42 +419,39 @@
         <v>問題番号</v>
       </c>
       <c r="B1" t="str">
-        <v>科目</v>
+        <v>タグ</v>
       </c>
       <c r="C1" t="str">
-        <v>タグ</v>
+        <v>問題文</v>
       </c>
       <c r="D1" t="str">
-        <v>問題文</v>
+        <v>下線キーワード</v>
       </c>
       <c r="E1" t="str">
-        <v>下線キーワード</v>
+        <v>画像URL</v>
       </c>
       <c r="F1" t="str">
-        <v>画像URL</v>
+        <v>選択肢a</v>
       </c>
       <c r="G1" t="str">
-        <v>選択肢a</v>
+        <v>選択肢b</v>
       </c>
       <c r="H1" t="str">
-        <v>選択肢b</v>
+        <v>選択肢c</v>
       </c>
       <c r="I1" t="str">
-        <v>選択肢c</v>
+        <v>選択肢d</v>
       </c>
       <c r="J1" t="str">
-        <v>選択肢d</v>
+        <v>選択肢e</v>
       </c>
       <c r="K1" t="str">
-        <v>選択肢e</v>
+        <v>正解</v>
       </c>
       <c r="L1" t="str">
-        <v>正解</v>
+        <v>解説</v>
       </c>
       <c r="M1" t="str">
-        <v>解説</v>
-      </c>
-      <c r="N1" t="str">
         <v>基本事項</v>
       </c>
     </row>
@@ -464,42 +460,39 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>循環器</v>
+        <v>心電図、虚血性心疾患</v>
       </c>
       <c r="C2" t="str">
-        <v>心電図、虚血性心疾患</v>
+        <v>急性心筋梗塞の発症直後（超急性期）にみられる心電図変化として、最も特徴的なのはどれか。</v>
       </c>
       <c r="D2" t="str">
-        <v>急性心筋梗塞の発症直後（超急性期）にみられる心電図変化として、最も特徴的なのはどれか。</v>
+        <v>超急性期、心電図変化</v>
       </c>
       <c r="E2" t="str">
-        <v>超急性期、心電図変化</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>ST上昇</v>
       </c>
       <c r="G2" t="str">
-        <v>ST上昇</v>
+        <v>異常Q波の出現</v>
       </c>
       <c r="H2" t="str">
-        <v>異常Q波の出現</v>
+        <v>T波の陰転化</v>
       </c>
       <c r="I2" t="str">
-        <v>T波の陰転化</v>
+        <v>PQ間隔の延長</v>
       </c>
       <c r="J2" t="str">
-        <v>PQ間隔の延長</v>
+        <v>U波の出現</v>
       </c>
       <c r="K2" t="str">
-        <v>U波の出現</v>
+        <v>a</v>
       </c>
       <c r="L2" t="str">
-        <v>a</v>
-      </c>
-      <c r="M2" t="str">
         <v>急性心筋梗塞の超急性期には、障害を受けた心筋領域に一致した誘導でST上昇が最初に出現する。異常Q波やT波の陰転化は、より後の時期（急性期〜亜急性期）にみられる所見である。</v>
       </c>
-      <c r="N2" t="str" xml:space="preserve">
+      <c r="M2" t="str" xml:space="preserve">
         <v xml:space="preserve">ST上昇 → 異常Q波 → 陰転化したT波、という経時的変化を覚える
 ST上昇は障害心筋に一致した誘導に出現する
 異常Q波は不可逆的な心筋壊死を反映する</v>
@@ -510,42 +503,39 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>消化器</v>
+        <v>肝臓、生理学</v>
       </c>
       <c r="C3" t="str">
-        <v>肝臓、生理学</v>
+        <v>肝臓の機能に関する記述のうち、誤っているのはどれか。</v>
       </c>
       <c r="D3" t="str">
-        <v>肝臓の機能に関する記述のうち、誤っているのはどれか。</v>
+        <v>肝臓の機能</v>
       </c>
       <c r="E3" t="str">
-        <v>肝臓の機能</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>アルブミンを合成する</v>
       </c>
       <c r="G3" t="str">
-        <v>アルブミンを合成する</v>
+        <v>胆汁を生成する</v>
       </c>
       <c r="H3" t="str">
-        <v>胆汁を生成する</v>
+        <v>胆汁を貯留する</v>
       </c>
       <c r="I3" t="str">
-        <v>胆汁を貯留する</v>
+        <v>アンモニアを尿素に変換する</v>
       </c>
       <c r="J3" t="str">
-        <v>アンモニアを尿素に変換する</v>
+        <v>薬物を代謝する</v>
       </c>
       <c r="K3" t="str">
-        <v>薬物を代謝する</v>
+        <v>c</v>
       </c>
       <c r="L3" t="str">
-        <v>c</v>
-      </c>
-      <c r="M3" t="str">
         <v>胆汁は肝細胞で生成されるが、貯留し濃縮するのは胆嚢の役割である。肝臓はアルブミン合成、尿素回路によるアンモニア処理、薬物代謝など多彩な機能を担う。</v>
       </c>
-      <c r="N3" t="str" xml:space="preserve">
+      <c r="M3" t="str" xml:space="preserve">
         <v xml:space="preserve">胆汁の生成は肝臓、貯留・濃縮は胆嚢と区別する
 肝臓は合成・解毒・代謝の中心臓器
 アンモニアは尿素回路で尿素に変換され腎から排泄される</v>
@@ -556,42 +546,39 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>代謝・内分泌</v>
+        <v>糖尿病、検査値</v>
       </c>
       <c r="C4" t="str">
-        <v>糖尿病、検査値</v>
+        <v>空腹時血糖値が糖尿病型と判定される基準値はどれか。</v>
       </c>
       <c r="D4" t="str">
-        <v>空腹時血糖値が糖尿病型と判定される基準値はどれか。</v>
+        <v>空腹時血糖値</v>
       </c>
       <c r="E4" t="str">
-        <v>空腹時血糖値</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>100 mg/dL以上</v>
       </c>
       <c r="G4" t="str">
-        <v>100 mg/dL以上</v>
+        <v>110 mg/dL以上</v>
       </c>
       <c r="H4" t="str">
-        <v>110 mg/dL以上</v>
+        <v>126 mg/dL以上</v>
       </c>
       <c r="I4" t="str">
-        <v>126 mg/dL以上</v>
+        <v>140 mg/dL以上</v>
       </c>
       <c r="J4" t="str">
-        <v>140 mg/dL以上</v>
+        <v>200 mg/dL以上</v>
       </c>
       <c r="K4" t="str">
-        <v>200 mg/dL以上</v>
+        <v>c</v>
       </c>
       <c r="L4" t="str">
-        <v>c</v>
-      </c>
-      <c r="M4" t="str">
         <v>空腹時血糖値126 mg/dL以上、または75gOGTT2時間値200 mg/dL以上、随時血糖値200 mg/dL以上のいずれかを満たす場合を糖尿病型と判定する。</v>
       </c>
-      <c r="N4" t="str" xml:space="preserve">
+      <c r="M4" t="str" xml:space="preserve">
         <v xml:space="preserve">空腹時血糖126以上／OGTT2時間値200以上／随時血糖200以上のいずれかで糖尿病型
 正常型は空腹時110未満かつOGTT2時間値140未満
 境界型はそのいずれにも属さない中間域</v>
@@ -602,42 +589,39 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>薬理</v>
+        <v>抗菌薬、副作用</v>
       </c>
       <c r="C5" t="str">
-        <v>抗菌薬、副作用</v>
+        <v>アミノグリコシド系抗菌薬で頻度の高い重大な副作用はどれか。</v>
       </c>
       <c r="D5" t="str">
-        <v>アミノグリコシド系抗菌薬で頻度の高い重大な副作用はどれか。</v>
+        <v>アミノグリコシド系抗菌薬</v>
       </c>
       <c r="E5" t="str">
-        <v>アミノグリコシド系抗菌薬</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>腎障害・第8脳神経障害</v>
       </c>
       <c r="G5" t="str">
-        <v>腎障害・第8脳神経障害</v>
+        <v>肝障害</v>
       </c>
       <c r="H5" t="str">
-        <v>肝障害</v>
+        <v>骨髄抑制</v>
       </c>
       <c r="I5" t="str">
-        <v>骨髄抑制</v>
+        <v>光線過敏症</v>
       </c>
       <c r="J5" t="str">
-        <v>光線過敏症</v>
+        <v>消化管出血</v>
       </c>
       <c r="K5" t="str">
-        <v>消化管出血</v>
+        <v>a</v>
       </c>
       <c r="L5" t="str">
-        <v>a</v>
-      </c>
-      <c r="M5" t="str">
         <v>アミノグリコシド系抗菌薬は腎尿細管への蓄積による腎障害と、内耳への蓄積による第8脳神経障害（聴力障害・平衡障害）が代表的な副作用である。</v>
       </c>
-      <c r="N5" t="str" xml:space="preserve">
+      <c r="M5" t="str" xml:space="preserve">
         <v xml:space="preserve">腎機能と聴力のモニタリングが投与中に重要
 血中濃度モニタリング（TDM）の対象薬
 高齢者・腎機能低下患者では特に注意</v>
@@ -648,42 +632,39 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>呼吸器</v>
+        <v>喘息、治療</v>
       </c>
       <c r="C6" t="str">
-        <v>喘息、治療</v>
+        <v>気管支喘息の長期管理薬として適切なのはどれか。2つ選べ。</v>
       </c>
       <c r="D6" t="str">
-        <v>気管支喘息の長期管理薬として適切なのはどれか。2つ選べ。</v>
+        <v>長期管理薬</v>
       </c>
       <c r="E6" t="str">
-        <v>長期管理薬</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>吸入ステロイド薬</v>
       </c>
       <c r="G6" t="str">
-        <v>吸入ステロイド薬</v>
+        <v>短時間作用性β2刺激薬</v>
       </c>
       <c r="H6" t="str">
-        <v>短時間作用性β2刺激薬</v>
+        <v>ロイコトリエン受容体拮抗薬</v>
       </c>
       <c r="I6" t="str">
-        <v>ロイコトリエン受容体拮抗薬</v>
+        <v>アドレナリン皮下注射</v>
       </c>
       <c r="J6" t="str">
-        <v>アドレナリン皮下注射</v>
+        <v>生理食塩水吸入</v>
       </c>
       <c r="K6" t="str">
-        <v>生理食塩水吸入</v>
+        <v>a、c</v>
       </c>
       <c r="L6" t="str">
-        <v>a、c</v>
-      </c>
-      <c r="M6" t="str">
         <v>長期管理薬（コントローラー）の中心は吸入ステロイド薬であり、ロイコトリエン受容体拮抗薬も併用される。短時間作用性β2刺激薬やアドレナリンは発作時に使う発作治療薬（リリーバー）である。</v>
       </c>
-      <c r="N6" t="str" xml:space="preserve">
+      <c r="M6" t="str" xml:space="preserve">
         <v xml:space="preserve">長期管理薬（コントローラー）と発作治療薬（リリーバー）を区別する
 吸入ステロイド薬が長期管理の基本
 短時間作用性β2刺激薬の使用頻度はコントロール状態の指標になる</v>
@@ -691,7 +672,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>